--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_12/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_12/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>69.06</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15.18</v>
       </c>
       <c r="E2" t="n">
-        <v>23.18</v>
+        <v>20.5</v>
       </c>
       <c r="F2" t="n">
-        <v>50.24</v>
+        <v>52.55</v>
       </c>
       <c r="G2" t="n">
-        <v>54.64</v>
+        <v>60.01</v>
       </c>
       <c r="H2" t="n">
-        <v>65.16</v>
+        <v>72.69</v>
       </c>
       <c r="I2" t="n">
-        <v>81.01000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>49.76</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>47.24</v>
+        <v>44.78</v>
       </c>
       <c r="D3" t="n">
-        <v>0.71</v>
+        <v>1.82</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5</v>
+        <v>4.06</v>
       </c>
       <c r="F3" t="n">
-        <v>44.63</v>
+        <v>40.91</v>
       </c>
       <c r="G3" t="n">
-        <v>47.48</v>
+        <v>45.51</v>
       </c>
       <c r="H3" t="n">
-        <v>47.5</v>
+        <v>45.53</v>
       </c>
       <c r="I3" t="n">
-        <v>47.54</v>
+        <v>45.56</v>
       </c>
       <c r="J3" t="n">
-        <v>47.87</v>
+        <v>47.32</v>
       </c>
       <c r="K3" t="n">
-        <v>3.24</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>9.140000000000001</v>
+        <v>10.28</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="E4" t="n">
-        <v>19.69</v>
+        <v>19.68</v>
       </c>
       <c r="F4" t="n">
-        <v>6.91</v>
+        <v>7.23</v>
       </c>
       <c r="G4" t="n">
-        <v>7.77</v>
+        <v>8.51</v>
       </c>
       <c r="H4" t="n">
-        <v>8.119999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="I4" t="n">
-        <v>10.87</v>
+        <v>11.94</v>
       </c>
       <c r="J4" t="n">
-        <v>12.19</v>
+        <v>13.54</v>
       </c>
       <c r="K4" t="n">
-        <v>5.28</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>104.11</v>
+        <v>113.55</v>
       </c>
       <c r="D5" t="n">
-        <v>23.04</v>
+        <v>48.68</v>
       </c>
       <c r="E5" t="n">
-        <v>22.13</v>
+        <v>42.87</v>
       </c>
       <c r="F5" t="n">
-        <v>74.29000000000001</v>
+        <v>52.67</v>
       </c>
       <c r="G5" t="n">
-        <v>91.14</v>
+        <v>64</v>
       </c>
       <c r="H5" t="n">
-        <v>96.53</v>
+        <v>115.55</v>
       </c>
       <c r="I5" t="n">
-        <v>105.55</v>
+        <v>154.35</v>
       </c>
       <c r="J5" t="n">
-        <v>171.42</v>
+        <v>175.73</v>
       </c>
       <c r="K5" t="n">
-        <v>97.13</v>
+        <v>123.07</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>2.96</v>
+        <v>3.76</v>
       </c>
       <c r="D6" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>8.77</v>
+        <v>13.36</v>
       </c>
       <c r="F6" t="n">
-        <v>2.54</v>
+        <v>3.19</v>
       </c>
       <c r="G6" t="n">
-        <v>2.71</v>
+        <v>3.37</v>
       </c>
       <c r="H6" t="n">
-        <v>2.99</v>
+        <v>3.58</v>
       </c>
       <c r="I6" t="n">
-        <v>3.09</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
-        <v>3.42</v>
+        <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>0.88</v>
+        <v>1.71</v>
       </c>
     </row>
   </sheetData>
